--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128782366</v>
       </c>
       <c r="B2" t="n">
-        <v>105745</v>
+        <v>105750</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128782366</v>
       </c>
       <c r="B2" t="n">
-        <v>105750</v>
+        <v>105778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128782366</v>
       </c>
       <c r="B2" t="n">
-        <v>105778</v>
+        <v>105784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128782366</v>
       </c>
       <c r="B2" t="n">
-        <v>105784</v>
+        <v>105791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128782366</v>
       </c>
       <c r="B2" t="n">
-        <v>105791</v>
+        <v>105795</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128782366</v>
       </c>
       <c r="B2" t="n">
-        <v>105795</v>
+        <v>105802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128782366</v>
       </c>
       <c r="B2" t="n">
-        <v>105810</v>
+        <v>105815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128782366</v>
       </c>
       <c r="B2" t="n">
-        <v>105815</v>
+        <v>105818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128782366</v>
       </c>
       <c r="B2" t="n">
-        <v>105818</v>
+        <v>105828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128782366</v>
+        <v>129317708</v>
       </c>
       <c r="B2" t="n">
-        <v>105828</v>
+        <v>105835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jörgen Petersson, Brita Svensson, Bengt Carlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129317708</v>
       </c>
       <c r="B2" t="n">
-        <v>105835</v>
+        <v>105837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129317708</v>
       </c>
       <c r="B2" t="n">
-        <v>105837</v>
+        <v>105863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129317708</v>
       </c>
       <c r="B2" t="n">
-        <v>105863</v>
+        <v>105865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Brita Svensson, Bengt Carlsson</t>
+          <t>Bengt Carlsson, Brita Svensson, Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129317708</v>
       </c>
       <c r="B2" t="n">
-        <v>105865</v>
+        <v>105866</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Carlsson, Brita Svensson, Jörgen Petersson</t>
+          <t>Jörgen Petersson, Brita Svensson, Bengt Carlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129317708</v>
       </c>
       <c r="B2" t="n">
-        <v>105866</v>
+        <v>105870</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129317708</v>
       </c>
       <c r="B2" t="n">
-        <v>105870</v>
+        <v>105872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Brita Svensson, Bengt Carlsson</t>
+          <t>Bengt Carlsson, Brita Svensson, Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129317708</v>
       </c>
       <c r="B2" t="n">
-        <v>105872</v>
+        <v>105876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Carlsson, Brita Svensson, Jörgen Petersson</t>
+          <t>Jörgen Petersson, Brita Svensson, Bengt Carlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129317708</v>
       </c>
       <c r="B2" t="n">
-        <v>105876</v>
+        <v>105886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129317708</v>
       </c>
       <c r="B2" t="n">
-        <v>105886</v>
+        <v>105889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Brita Svensson, Bengt Carlsson</t>
+          <t>Bengt Carlsson, Brita Svensson, Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Carlsson, Brita Svensson, Jörgen Petersson</t>
+          <t>Jörgen Petersson, Brita Svensson, Bengt Carlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129317708</v>
       </c>
       <c r="B2" t="n">
-        <v>105889</v>
+        <v>105918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129317708</v>
       </c>
       <c r="B2" t="n">
-        <v>105918</v>
+        <v>105930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129317708</v>
       </c>
       <c r="B2" t="n">
-        <v>105930</v>
+        <v>105931</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129317708</v>
       </c>
       <c r="B2" t="n">
-        <v>105931</v>
+        <v>105936</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129317708</v>
       </c>
       <c r="B2" t="n">
-        <v>105936</v>
+        <v>106340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,6 +783,117 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129317709</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106340</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>671</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gotlandsmåra</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Galium rotundifolium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Norrbys 1:14 (5), GGN-bana, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>705261</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6394011</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hejdeby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Endurobana.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson, Brita Svensson, Bengt Carlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22883-2024 artfynd.xlsx
+++ b/artfynd/A 22883-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317708</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317709</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>